--- a/datasets/IndicWikiQA-Tam_EN.xlsx
+++ b/datasets/IndicWikiQA-Tam_EN.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="639">
-  <si>
-    <t>question</t>
-  </si>
-  <si>
-    <t>gold_answer</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="633">
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Answer</t>
   </si>
   <si>
     <t>Wikipedia Page</t>
   </si>
   <si>
-    <t>domain</t>
+    <t>Domain</t>
   </si>
   <si>
     <t>Which steamed cake, made from a fermented batter of rice and lentils, is a staple breakfast in Tamil Nadu?</t>
@@ -193,7 +196,7 @@
     <t>What is the traditional Tamil term for a spicy, tempered mango pickle?</t>
   </si>
   <si>
-    <t>Maangai Oorkai</t>
+    <t>Maangai Oorkai (Mango Pickle)</t>
   </si>
   <si>
     <t>https://en.wikipedia.org/wiki/Mango_pickle</t>
@@ -262,19 +265,10 @@
     <t>https://en.wikipedia.org/wiki/Tamil_cuisine</t>
   </si>
   <si>
-    <t>Which intensely spicy meat dish, heavily flavored with black pepper, star anise, and roasted spices, is a hallmark of the Nattukotai Chettiar community?</t>
-  </si>
-  <si>
-    <t>Chettinad Mutton</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/wiki/Chettinad_cuisine</t>
-  </si>
-  <si>
     <t>What is the simple, thick boiled lentil preparation often mixed with rice and ghee at the beginning of a traditional Tamil meal?</t>
   </si>
   <si>
-    <t>Paruppu</t>
+    <t>Dal</t>
   </si>
   <si>
     <t>https://en.wikipedia.org/wiki/Dal</t>
@@ -310,7 +304,7 @@
     <t>Which traditional sweet flatbread, stuffed with a mixture of chana dal, jaggery, and coconut, is popular in Tamil Nadu during festivals?</t>
   </si>
   <si>
-    <t>Poli</t>
+    <t>Boli</t>
   </si>
   <si>
     <t>https://en.wikipedia.org/wiki/Obbattu</t>
@@ -331,7 +325,7 @@
     <t>Thengai Chutney</t>
   </si>
   <si>
-    <t>https://en.wikipedia.org/wiki/Chutney</t>
+    <t>https://en.wikipedia.org/wiki/Coconut_chutney</t>
   </si>
   <si>
     <t>Which harvest festival is widely celebrated by Tamils in mid-January?</t>
@@ -436,7 +430,7 @@
     <t>Which classic sweet, sour, and bitter dish made from raw mango and neem flowers is prepared on Puthandu?</t>
   </si>
   <si>
-    <t>Maangai Pachadi</t>
+    <t>Maangai Pachadi (Mango Pachadi)</t>
   </si>
   <si>
     <t>Which festival heavily honors the god Murugan with devotees carrying physical burdens called kavadi?</t>
@@ -571,7 +565,7 @@
     <t>Which sweet, steamed dumpling is traditionally offered to Pillayar during his festival?</t>
   </si>
   <si>
-    <t>Mothagam</t>
+    <t>Modagam</t>
   </si>
   <si>
     <t>What tiered, thematic doll display is a central tradition in Tamil households during Navaratri?</t>
@@ -580,7 +574,7 @@
     <t>Bommai Golu</t>
   </si>
   <si>
-    <t>https://en.wikipedia.org/wiki/Golu</t>
+    <t>https://en.wikipedia.org/wiki/Golu_(festival)</t>
   </si>
   <si>
     <t>Which special prayer day occurs during Navaratri to honor the Goddess of Knowledge?</t>
@@ -607,21 +601,15 @@
     <t>https://en.wikipedia.org/wiki/Vijayadashami</t>
   </si>
   <si>
-    <t>What specific, early-morning oil bath tradition is a hallmark of Tamil Deepavali celebrations?</t>
-  </si>
-  <si>
-    <t>Ganga Snanam</t>
+    <t>Which mythological demon's defeat by Lord Krishna is the primary reason South Indians celebrate Deepavali?</t>
+  </si>
+  <si>
+    <t>Narakasura</t>
   </si>
   <si>
     <t>https://en.wikipedia.org/wiki/Diwali</t>
   </si>
   <si>
-    <t>Which mythological demon's defeat by Lord Krishna is the primary reason South Indians celebrate Deepavali?</t>
-  </si>
-  <si>
-    <t>Narakasura</t>
-  </si>
-  <si>
     <t>Which rural goddess of weather, medicine, and fertility is celebrated heavily in village festivals?</t>
   </si>
   <si>
@@ -670,7 +658,7 @@
     <t>What is the grand event in Tamil temple festivals where the deity is pulled through the streets in a massive wooden chariot?</t>
   </si>
   <si>
-    <t>Ther Thiruvizha (Temple Car Festival)</t>
+    <t>Temple Car Festival (Ther)</t>
   </si>
   <si>
     <t>https://en.wikipedia.org/wiki/Temple_car</t>
@@ -679,7 +667,7 @@
     <t>What large, natural leaf is customarily used as a plate to serve multi-course festival meals?</t>
   </si>
   <si>
-    <t>Vazhai Ilai (Banana Leaf)</t>
+    <t>Banana Leaf</t>
   </si>
   <si>
     <t>https://en.wikipedia.org/wiki/Banana_leaf</t>
@@ -694,10 +682,10 @@
     <t>https://en.wikipedia.org/wiki/Vibhuti</t>
   </si>
   <si>
-    <t>Which animal serves as the traditional vehicle or mount (Vahanam) for Lord Murugan during temple processions?</t>
-  </si>
-  <si>
-    <t>Peacock (Mayil)</t>
+    <t>Which animal serves as the traditional vehicle or mount for Lord Murugan during temple processions?</t>
+  </si>
+  <si>
+    <t>Peacock</t>
   </si>
   <si>
     <t>https://en.wikipedia.org/wiki/Vahana</t>
@@ -715,7 +703,7 @@
     <t>What type of ritual pot is carried by devotees, often balanced on their heads, as an offering during Murugan festivals?</t>
   </si>
   <si>
-    <t>Paal Kudam (Milk Pot)</t>
+    <t>Milk Pot</t>
   </si>
   <si>
     <t>What circular folk dance, performed by women clapping their hands rhythmically, is common in Tamil village festivals?</t>
@@ -814,7 +802,7 @@
     <t>What type of marriage reform in Tamil Nadu, legalized in 1967, allowed couples to marry without traditional Brahmin priests or religious rituals?</t>
   </si>
   <si>
-    <t>Self-Respect marriage (Suya Mariyathai)</t>
+    <t>Self-Respect marriage (Suyamariyathai)</t>
   </si>
   <si>
     <t>What British crown colony (now modern-day Sri Lanka) brought thousands of Tamils from India for plantation work in the 19th and 20th centuries?</t>
@@ -830,9 +818,6 @@
   </si>
   <si>
     <t>Tea</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/wiki/Tea_production_in_Sri_Lanka</t>
   </si>
   <si>
     <t>What ancient bull-taming sport, with roots tracing back to the Tamil classical period, is traditionally practiced during the Pongal festival?</t>
@@ -1933,31 +1918,42 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FF0000ff"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
-      <color rgb="FF1155CC"/>
+      <sz val="11"/>
+      <color rgb="FF1155cc"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1965,58 +1961,68 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="6">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -2043,22 +2049,82 @@
         <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2070,4320 +2136,3304 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:D223"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="12.63"/>
+    <col min="1" max="1" style="5" width="135.57642857142858" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="56.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="5" width="26.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="21.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+      <c r="A18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+      <c r="A22" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+      <c r="A23" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+      <c r="A24" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+      <c r="A29" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+      <c r="A30" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+      <c r="A31" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+      <c r="A32" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+      <c r="A33" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="17.25">
+      <c r="A34" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="3" t="s">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="17.25">
+      <c r="A35" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="17.25">
+      <c r="A36" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="17.25">
+      <c r="A37" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="17.25">
+      <c r="A38" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="17.25">
+      <c r="A39" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="17.25">
+      <c r="A40" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="17.25">
+      <c r="A41" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="17.25">
+      <c r="A42" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="17.25">
+      <c r="A43" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="17.25">
+      <c r="A44" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="17.25">
+      <c r="A45" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="17.25">
+      <c r="A46" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3" t="s">
+      <c r="D46" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="17.25">
+      <c r="A47" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="3" t="s">
+      <c r="D47" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="17.25">
+      <c r="A48" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="17.25">
+      <c r="A49" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="17.25">
+      <c r="A50" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="17.25">
+      <c r="A51" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="3" t="s">
+      <c r="D51" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="17.25">
+      <c r="A52" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="17.25">
+      <c r="A53" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="3" t="s">
+      <c r="D53" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="17.25">
+      <c r="A54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="17.25">
+      <c r="A55" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3" t="s">
+      <c r="D55" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="17.25">
+      <c r="A56" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="17.25">
+      <c r="A57" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="17.25">
+      <c r="A58" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="17.25">
+      <c r="A59" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="3" t="s">
+      <c r="D59" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="17.25">
+      <c r="A60" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="3" t="s">
+      <c r="D60" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="17.25">
+      <c r="A61" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="17.25">
+      <c r="A62" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="17.25">
+      <c r="A63" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3" t="s">
+      <c r="D63" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="17.25">
+      <c r="A64" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="3" t="s">
+      <c r="D64" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="17.25">
+      <c r="A65" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3" t="s">
+      <c r="D65" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="17.25">
+      <c r="A66" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="17.25">
+      <c r="A67" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="3" t="s">
+      <c r="D67" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="17.25">
+      <c r="A68" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="17.25">
+      <c r="A69" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3" t="s">
+      <c r="D69" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="17.25">
+      <c r="A70" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="3" t="s">
+      <c r="D70" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="17.25">
+      <c r="A71" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="17.25">
+      <c r="A72" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="3" t="s">
+      <c r="D72" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="17.25">
+      <c r="A73" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="3" t="s">
+      <c r="D73" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="17.25">
+      <c r="A74" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="3" t="s">
+      <c r="D74" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="17.25">
+      <c r="A75" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="D75" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="17.25">
+      <c r="A76" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="B76" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="D76" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="17.25">
+      <c r="A77" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="B77" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="D77" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="17.25">
+      <c r="A78" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="B78" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="D78" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="17.25">
+      <c r="A79" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="B79" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="D79" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="17.25">
+      <c r="A80" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="B80" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="D80" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="17.25">
+      <c r="A81" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="B81" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="D81" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="17.25">
+      <c r="A82" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="B82" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="D82" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="17.25">
+      <c r="A83" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="B83" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="D83" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="17.25">
+      <c r="A84" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="B84" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="3" t="s">
+      <c r="C84" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="17.25">
+      <c r="A85" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="3" t="s">
+      <c r="D85" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="17.25">
+      <c r="A86" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="D86" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="17.25">
+      <c r="A87" s="2" t="s">
         <v>236</v>
       </c>
+      <c r="B87" s="2" t="s">
+        <v>237</v>
+      </c>
       <c r="C87" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>239</v>
       </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="17.25">
+      <c r="A88" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>241</v>
+      </c>
       <c r="C88" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B89" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="D88" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="17.25">
+      <c r="A89" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="B89" s="2" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="5" t="s">
+      <c r="C89" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="D89" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="17.25">
+      <c r="A90" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="B90" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D90" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="5" t="s">
+      <c r="C90" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="17.25">
+      <c r="A91" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="17.25">
+      <c r="A92" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D91" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="5" t="s">
+      <c r="B92" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="C92" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="17.25">
+      <c r="A93" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C92" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="5" t="s">
+      <c r="B93" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="B93" s="5" t="s">
+      <c r="C93" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C93" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="5" t="s">
+      <c r="D93" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="17.25">
+      <c r="A94" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C94" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="5" t="s">
+      <c r="C94" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="B95" s="5" t="s">
+      <c r="D94" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="17.25">
+      <c r="A95" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="B95" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="5" t="s">
+      <c r="C95" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="D95" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="17.25">
+      <c r="A96" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="B96" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D96" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="5" t="s">
+      <c r="C96" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="17.25">
+      <c r="A97" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C97" s="6" t="s">
+      <c r="C97" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="D97" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="5" t="s">
+      <c r="D97" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="17.25">
+      <c r="A98" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="5" t="s">
+      <c r="C98" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="17.25">
+      <c r="A99" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="17.25">
+      <c r="A100" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C99" s="6" t="s">
+      <c r="B100" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="D99" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="5" t="s">
+      <c r="C100" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="D100" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="17.25">
+      <c r="A101" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="B101" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="D100" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="5" t="s">
+      <c r="C101" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="B101" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="5" t="s">
+      <c r="D101" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="17.25">
+      <c r="A102" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="D102" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="G102" s="5"/>
-      <c r="H102" s="5"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="5"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="5" t="s">
+      <c r="D102" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="17.25">
+      <c r="A103" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C103" s="6" t="s">
+      <c r="C103" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="D103" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="5"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="5" t="s">
+      <c r="D103" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="17.25">
+      <c r="A104" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C104" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="5"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="5" t="s">
+      <c r="D104" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="17.25">
+      <c r="A105" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C105" s="6" t="s">
+      <c r="C105" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D105" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="5"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B106" s="5" t="s">
+      <c r="D105" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="17.25">
+      <c r="A106" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C106" s="6" t="s">
+      <c r="B106" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="D106" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="5"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="5" t="s">
+      <c r="C106" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="D106" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="17.25">
+      <c r="A107" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="B107" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D107" s="5" t="s">
+      <c r="C107" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="5" t="s">
+      <c r="D107" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="17.25">
+      <c r="A108" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="D108" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="5" t="s">
+      <c r="D108" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="17.25">
+      <c r="A109" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C109" s="6" t="s">
+      <c r="C109" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D109" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="5" t="s">
+      <c r="D109" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="17.25">
+      <c r="A110" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B110" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C110" s="6" t="s">
+      <c r="C110" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D110" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="5" t="s">
+      <c r="D110" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="17.25">
+      <c r="A111" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B111" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="C111" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="D111" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="5" t="s">
+      <c r="D111" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="17.25">
+      <c r="A112" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B112" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C112" s="6" t="s">
+      <c r="C112" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="D112" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="5" t="s">
+      <c r="D112" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="17.25">
+      <c r="A113" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="B113" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C113" s="6" t="s">
+      <c r="C113" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="D113" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="5" t="s">
+      <c r="D113" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="17.25">
+      <c r="A114" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="B114" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C114" s="6" t="s">
+      <c r="C114" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="D114" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="5" t="s">
+      <c r="D114" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="17.25">
+      <c r="A115" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="17.25">
+      <c r="A116" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="B116" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D115" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="5" t="s">
+      <c r="C116" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="D116" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="17.25">
+      <c r="A117" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C116" s="6" t="s">
+      <c r="B117" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D116" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="5" t="s">
+      <c r="C117" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="B117" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="5" t="s">
+      <c r="D117" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="17.25">
+      <c r="A118" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="C118" s="6" t="s">
+      <c r="C118" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="D118" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="5" t="s">
+      <c r="D118" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="17.25">
+      <c r="A119" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B119" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="D119" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="5" t="s">
+      <c r="D119" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="17.25">
+      <c r="A120" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B120" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C120" s="6" t="s">
+      <c r="C120" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="D120" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="5" t="s">
+      <c r="D120" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="17.25">
+      <c r="A121" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="B121" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="C121" s="6" t="s">
+      <c r="C121" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D121" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="5" t="s">
+      <c r="D121" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="17.25">
+      <c r="A122" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B122" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="C122" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D122" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="5" t="s">
+      <c r="D122" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="17.25">
+      <c r="A123" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B123" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="C123" s="6" t="s">
+      <c r="C123" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="D123" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="5" t="s">
+      <c r="D123" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="17.25">
+      <c r="A124" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B124" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="C124" s="6" t="s">
+      <c r="C124" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="D124" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="5" t="s">
+      <c r="D124" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="17.25">
+      <c r="A125" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B125" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C125" s="6" t="s">
+      <c r="C125" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="D125" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="5" t="s">
+      <c r="D125" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="17.25">
+      <c r="A126" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B126" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C126" s="6" t="s">
+      <c r="C126" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="D126" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="5" t="s">
+      <c r="D126" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="17.25">
+      <c r="A127" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B127" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="C127" s="6" t="s">
+      <c r="C127" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="D127" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="5" t="s">
+      <c r="D127" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="17.25">
+      <c r="A128" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B128" s="5" t="s">
+      <c r="B128" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="C128" s="6" t="s">
+      <c r="C128" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="D128" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="5" t="s">
+      <c r="D128" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="17.25">
+      <c r="A129" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B129" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="C129" s="6" t="s">
+      <c r="C129" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="D129" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="5" t="s">
+      <c r="D129" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="17.25">
+      <c r="A130" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B130" s="5" t="s">
+      <c r="B130" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="C130" s="6" t="s">
+      <c r="C130" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="D130" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="5" t="s">
+      <c r="D130" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="17.25">
+      <c r="A131" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B131" s="5" t="s">
+      <c r="B131" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="C131" s="6" t="s">
+      <c r="C131" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="D131" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="5" t="s">
+      <c r="D131" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="17.25">
+      <c r="A132" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B132" s="5" t="s">
+      <c r="B132" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C132" s="6" t="s">
+      <c r="C132" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="D132" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="5" t="s">
+      <c r="D132" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="17.25">
+      <c r="A133" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B133" s="5" t="s">
+      <c r="B133" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="C133" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="D133" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="5" t="s">
+      <c r="D133" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="17.25">
+      <c r="A134" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B134" s="5" t="s">
+      <c r="B134" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="6" t="s">
+      <c r="C134" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="D134" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="5" t="s">
+      <c r="D134" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="17.25">
+      <c r="A135" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B135" s="5" t="s">
+      <c r="B135" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="C135" s="6" t="s">
+      <c r="C135" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="D135" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="5" t="s">
+      <c r="D135" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="17.25">
+      <c r="A136" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B136" s="5" t="s">
+      <c r="B136" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="C136" s="6" t="s">
+      <c r="C136" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="D136" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="5" t="s">
+      <c r="D136" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="17.25">
+      <c r="A137" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="B137" s="5" t="s">
+      <c r="B137" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C137" s="6" t="s">
+      <c r="C137" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="D137" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="5" t="s">
+      <c r="D137" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="17.25">
+      <c r="A138" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="B138" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C138" s="6" t="s">
+      <c r="C138" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="D138" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="5" t="s">
+      <c r="D138" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="17.25">
+      <c r="A139" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B139" s="5" t="s">
+      <c r="B139" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="C139" s="6" t="s">
+      <c r="C139" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="D139" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="5" t="s">
+      <c r="D139" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="17.25">
+      <c r="A140" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B140" s="5" t="s">
+      <c r="B140" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="C140" s="6" t="s">
+      <c r="C140" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="D140" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="5" t="s">
+      <c r="D140" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="17.25">
+      <c r="A141" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B141" s="5" t="s">
+      <c r="B141" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="C141" s="6" t="s">
+      <c r="C141" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="D141" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="5" t="s">
+      <c r="D141" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="17.25">
+      <c r="A142" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B142" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C142" s="6" t="s">
+      <c r="C142" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="17.25">
+      <c r="A143" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D142" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="5" t="s">
+      <c r="B143" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B143" s="5" t="s">
+      <c r="C143" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="D143" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="17.25">
+      <c r="A144" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D143" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="5" t="s">
+      <c r="B144" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="B144" s="5" t="s">
+      <c r="C144" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="C144" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="5" t="s">
+      <c r="D144" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="17.25">
+      <c r="A145" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B145" s="5" t="s">
+      <c r="B145" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C145" s="6" t="s">
+      <c r="C145" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="D145" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="5" t="s">
+      <c r="D145" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="17.25">
+      <c r="A146" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B146" s="5" t="s">
+      <c r="B146" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="C146" s="6" t="s">
+      <c r="C146" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="D146" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="5" t="s">
+      <c r="D146" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="17.25">
+      <c r="A147" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="B147" s="5" t="s">
+      <c r="B147" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="C147" s="6" t="s">
+      <c r="C147" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="D147" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="5" t="s">
+      <c r="D147" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="17.25">
+      <c r="A148" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B148" s="5" t="s">
+      <c r="B148" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="C148" s="6" t="s">
+      <c r="C148" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="D148" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="5" t="s">
+      <c r="D148" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="17.25">
+      <c r="A149" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B149" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C149" s="6" t="s">
+      <c r="C149" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="D149" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="5" t="s">
+      <c r="D149" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="17.25">
+      <c r="A150" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B150" s="5" t="s">
+      <c r="B150" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="C150" s="6" t="s">
+      <c r="C150" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="D150" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="5" t="s">
+      <c r="D150" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="17.25">
+      <c r="A151" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="B151" s="5" t="s">
+      <c r="B151" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="C151" s="6" t="s">
+      <c r="C151" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="D151" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="5" t="s">
+      <c r="D151" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="17.25">
+      <c r="A152" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B152" s="5" t="s">
+      <c r="B152" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="C152" s="6" t="s">
+      <c r="C152" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="D152" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="5" t="s">
+      <c r="D152" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="17.25">
+      <c r="A153" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B153" s="5" t="s">
+      <c r="B153" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="C153" s="6" t="s">
+      <c r="C153" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="D153" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="5" t="s">
+      <c r="D153" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="17.25">
+      <c r="A154" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="B154" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C154" s="6" t="s">
+      <c r="C154" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="D154" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="5" t="s">
+      <c r="D154" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="17.25">
+      <c r="A155" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B155" s="5" t="s">
+      <c r="B155" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="C155" s="6" t="s">
+      <c r="C155" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="D155" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="5" t="s">
+      <c r="D155" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="17.25">
+      <c r="A156" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="B156" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="C156" s="6" t="s">
+      <c r="C156" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="D156" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="5" t="s">
+      <c r="D156" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="17.25">
+      <c r="A157" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="B157" s="5" t="s">
+      <c r="B157" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="C157" s="6" t="s">
+      <c r="C157" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="D157" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="5" t="s">
+      <c r="D157" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="17.25">
+      <c r="A158" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="B158" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="C158" s="6" t="s">
+      <c r="C158" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D158" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="5" t="s">
+      <c r="D158" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="17.25">
+      <c r="A159" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="B159" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="C159" s="6" t="s">
+      <c r="C159" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D159" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="5" t="s">
+      <c r="D159" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="17.25">
+      <c r="A160" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B160" s="5" t="s">
+      <c r="B160" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="C160" s="6" t="s">
+      <c r="C160" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="D160" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="5" t="s">
+      <c r="D160" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="17.25">
+      <c r="A161" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B161" s="5" t="s">
+      <c r="B161" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="C161" s="6" t="s">
+      <c r="C161" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="D161" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="5" t="s">
+      <c r="D161" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="17.25">
+      <c r="A162" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B162" s="5" t="s">
+      <c r="B162" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="C162" s="6" t="s">
+      <c r="C162" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D162" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="5" t="s">
+      <c r="D162" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="17.25">
+      <c r="A163" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B163" s="5" t="s">
+      <c r="B163" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="C163" s="6" t="s">
+      <c r="C163" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="D163" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="5" t="s">
+      <c r="D163" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="17.25">
+      <c r="A164" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B164" s="5" t="s">
+      <c r="B164" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="C164" s="6" t="s">
+      <c r="C164" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D164" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="5" t="s">
+      <c r="D164" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="17.25">
+      <c r="A165" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B165" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="C165" s="6" t="s">
+      <c r="C165" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="D165" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="5" t="s">
+      <c r="D165" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="17.25">
+      <c r="A166" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B166" s="5" t="s">
+      <c r="B166" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="C166" s="6" t="s">
+      <c r="C166" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="D166" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="5" t="s">
+      <c r="D166" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="17.25">
+      <c r="A167" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="B167" s="5" t="s">
+      <c r="B167" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="C167" s="6" t="s">
+      <c r="C167" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="D167" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="5" t="s">
+      <c r="D167" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="17.25">
+      <c r="A168" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B168" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="C168" s="6" t="s">
+      <c r="C168" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="D168" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="5" t="s">
+      <c r="D168" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="17.25">
+      <c r="A169" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B169" s="5" t="s">
+      <c r="B169" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="C169" s="6" t="s">
+      <c r="C169" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="D169" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="5" t="s">
+      <c r="D169" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="17.25">
+      <c r="A170" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B170" s="5" t="s">
+      <c r="B170" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="C170" s="6" t="s">
+      <c r="C170" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="D170" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="5" t="s">
+      <c r="D170" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="17.25">
+      <c r="A171" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="B171" s="5" t="s">
+      <c r="B171" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C171" s="6" t="s">
+      <c r="C171" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="D171" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="5" t="s">
+      <c r="D171" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="17.25">
+      <c r="A172" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="B172" s="5" t="s">
+      <c r="B172" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C172" s="6" t="s">
+      <c r="C172" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="D172" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="5" t="s">
+      <c r="D172" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="17.25">
+      <c r="A173" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="B173" s="5" t="s">
+      <c r="B173" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="C173" s="6" t="s">
+      <c r="C173" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="D173" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="5" t="s">
+      <c r="D173" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="17.25">
+      <c r="A174" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="B174" s="5" t="s">
+      <c r="B174" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="C174" s="6" t="s">
+      <c r="C174" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="D174" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="5" t="s">
+      <c r="D174" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="17.25">
+      <c r="A175" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B175" s="5" t="s">
+      <c r="B175" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="C175" s="6" t="s">
+      <c r="C175" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="D175" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="5" t="s">
+      <c r="D175" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="176" customHeight="1" ht="17.25">
+      <c r="A176" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="B176" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C176" s="6" t="s">
+      <c r="C176" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="D176" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="5" t="s">
+      <c r="D176" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="177" customHeight="1" ht="17.25">
+      <c r="A177" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="B177" s="5" t="s">
+      <c r="B177" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="C177" s="6" t="s">
+      <c r="C177" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="D177" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="5" t="s">
+      <c r="D177" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="178" customHeight="1" ht="17.25">
+      <c r="A178" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B178" s="5" t="s">
+      <c r="B178" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C178" s="6" t="s">
+      <c r="C178" s="4" t="s">
         <v>503</v>
       </c>
-      <c r="D178" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="5" t="s">
+      <c r="D178" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="179" customHeight="1" ht="17.25">
+      <c r="A179" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="B179" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="C179" s="6" t="s">
+      <c r="C179" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="D179" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="5" t="s">
+      <c r="D179" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="180" customHeight="1" ht="17.25">
+      <c r="A180" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="B180" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C180" s="6" t="s">
+      <c r="C180" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="D180" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="5" t="s">
+      <c r="D180" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="181" customHeight="1" ht="17.25">
+      <c r="A181" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="B181" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="C181" s="6" t="s">
+      <c r="C181" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D181" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="5" t="s">
+      <c r="D181" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="182" customHeight="1" ht="17.25">
+      <c r="A182" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B182" s="5" t="s">
+      <c r="B182" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="C182" s="6" t="s">
+      <c r="C182" s="4" t="s">
         <v>515</v>
       </c>
-      <c r="D182" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="5" t="s">
+      <c r="D182" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="183" customHeight="1" ht="17.25">
+      <c r="A183" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="B183" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="C183" s="6" t="s">
+      <c r="C183" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="D183" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="5" t="s">
+      <c r="D183" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="184" customHeight="1" ht="17.25">
+      <c r="A184" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="B184" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C184" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="C184" s="6" t="s">
+      <c r="D184" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="185" customHeight="1" ht="17.25">
+      <c r="A185" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D184" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="5" t="s">
+      <c r="B185" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B185" s="5" t="s">
+      <c r="C185" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="C185" s="6" t="s">
+      <c r="D185" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="186" customHeight="1" ht="17.25">
+      <c r="A186" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D185" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="5" t="s">
+      <c r="B186" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="B186" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C186" s="6" t="s">
+      <c r="C186" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="D186" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="5" t="s">
+      <c r="D186" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="187" customHeight="1" ht="17.25">
+      <c r="A187" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="B187" s="5" t="s">
+      <c r="B187" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="C187" s="6" t="s">
+      <c r="C187" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D187" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="5" t="s">
+      <c r="D187" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="188" customHeight="1" ht="17.25">
+      <c r="A188" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B188" s="5" t="s">
+      <c r="B188" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C188" s="6" t="s">
+      <c r="C188" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="D188" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="5" t="s">
+      <c r="D188" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="189" customHeight="1" ht="17.25">
+      <c r="A189" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="B189" s="5" t="s">
+      <c r="B189" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C189" s="6" t="s">
+      <c r="C189" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="D189" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="5" t="s">
+      <c r="D189" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="190" customHeight="1" ht="17.25">
+      <c r="A190" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="B190" s="5" t="s">
+      <c r="B190" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="C190" s="6" t="s">
+      <c r="C190" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="D190" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="5" t="s">
+      <c r="D190" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="191" customHeight="1" ht="17.25">
+      <c r="A191" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="B191" s="5" t="s">
+      <c r="B191" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C191" s="6" t="s">
+      <c r="C191" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="D191" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="5" t="s">
+      <c r="D191" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="192" customHeight="1" ht="17.25">
+      <c r="A192" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B192" s="5" t="s">
+      <c r="B192" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="C192" s="6" t="s">
+      <c r="C192" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="D192" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="5" t="s">
+      <c r="D192" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="193" customHeight="1" ht="17.25">
+      <c r="A193" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="B193" s="5" t="s">
+      <c r="B193" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="C193" s="6" t="s">
+      <c r="C193" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="D193" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="5" t="s">
+      <c r="D193" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="194" customHeight="1" ht="17.25">
+      <c r="A194" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B194" s="5" t="s">
+      <c r="B194" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="C194" s="6" t="s">
+      <c r="C194" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="D194" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="5" t="s">
+      <c r="D194" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="195" customHeight="1" ht="17.25">
+      <c r="A195" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="B195" s="5" t="s">
+      <c r="B195" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="C195" s="6" t="s">
+      <c r="C195" s="4" t="s">
         <v>553</v>
       </c>
-      <c r="D195" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="5" t="s">
+      <c r="D195" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="196" customHeight="1" ht="17.25">
+      <c r="A196" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="B196" s="5" t="s">
+      <c r="B196" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C196" s="6" t="s">
+      <c r="C196" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="D196" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="5" t="s">
+      <c r="D196" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="197" customHeight="1" ht="17.25">
+      <c r="A197" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B197" s="5" t="s">
+      <c r="B197" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="C197" s="6" t="s">
+      <c r="C197" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="D197" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="5" t="s">
+      <c r="D197" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="198" customHeight="1" ht="17.25">
+      <c r="A198" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="B198" s="5" t="s">
+      <c r="B198" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="C198" s="6" t="s">
+      <c r="C198" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="D198" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="5" t="s">
+      <c r="D198" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="199" customHeight="1" ht="17.25">
+      <c r="A199" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="B199" s="5" t="s">
+      <c r="B199" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="C199" s="6" t="s">
+      <c r="C199" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="D199" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="5" t="s">
+      <c r="D199" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="200" customHeight="1" ht="17.25">
+      <c r="A200" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B200" s="5" t="s">
+      <c r="B200" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="C200" s="6" t="s">
+      <c r="C200" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="D200" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="5" t="s">
+      <c r="D200" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="201" customHeight="1" ht="17.25">
+      <c r="A201" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B201" s="5" t="s">
+      <c r="B201" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="C201" s="6" t="s">
+      <c r="C201" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="D201" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="5" t="s">
+      <c r="D201" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="202" customHeight="1" ht="17.25">
+      <c r="A202" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="B202" s="5" t="s">
+      <c r="B202" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="C202" s="6" t="s">
+      <c r="C202" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="D202" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="5" t="s">
+      <c r="D202" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="203" customHeight="1" ht="17.25">
+      <c r="A203" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B203" s="5" t="s">
+      <c r="B203" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="C203" s="6" t="s">
+      <c r="C203" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="D203" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="5" t="s">
+      <c r="D203" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="204" customHeight="1" ht="17.25">
+      <c r="A204" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="B204" s="5" t="s">
+      <c r="B204" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="C204" s="6" t="s">
+      <c r="C204" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="D204" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="5" t="s">
+      <c r="D204" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="205" customHeight="1" ht="17.25">
+      <c r="A205" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B205" s="5" t="s">
+      <c r="B205" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="C205" s="6" t="s">
+      <c r="C205" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="D205" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="5" t="s">
+      <c r="D205" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="206" customHeight="1" ht="17.25">
+      <c r="A206" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B206" s="5" t="s">
+      <c r="B206" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="C206" s="6" t="s">
+      <c r="C206" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="D206" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="5" t="s">
+      <c r="D206" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="207" customHeight="1" ht="17.25">
+      <c r="A207" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B207" s="5" t="s">
+      <c r="B207" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="C207" s="6" t="s">
+      <c r="C207" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="D207" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="5" t="s">
+      <c r="D207" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="208" customHeight="1" ht="17.25">
+      <c r="A208" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="B208" s="5" t="s">
+      <c r="B208" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="C208" s="6" t="s">
+      <c r="C208" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="D208" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="5" t="s">
+      <c r="D208" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="209" customHeight="1" ht="17.25">
+      <c r="A209" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B209" s="5" t="s">
+      <c r="B209" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="C209" s="6" t="s">
+      <c r="C209" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="D209" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="5" t="s">
+      <c r="D209" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="210" customHeight="1" ht="17.25">
+      <c r="A210" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="B210" s="5" t="s">
+      <c r="B210" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="C210" s="6" t="s">
+      <c r="C210" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="D210" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="5" t="s">
+      <c r="D210" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="211" customHeight="1" ht="17.25">
+      <c r="A211" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B211" s="5" t="s">
+      <c r="B211" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="C211" s="6" t="s">
+      <c r="C211" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="D211" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="5" t="s">
+      <c r="D211" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="212" customHeight="1" ht="17.25">
+      <c r="A212" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="B212" s="5" t="s">
+      <c r="B212" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="C212" s="6" t="s">
+      <c r="C212" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="213" customHeight="1" ht="17.25">
+      <c r="A213" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="D212" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="5" t="s">
+      <c r="B213" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="B213" s="5" t="s">
+      <c r="C213" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="C213" s="6" t="s">
+      <c r="D213" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="214" customHeight="1" ht="17.25">
+      <c r="A214" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="D213" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="5" t="s">
+      <c r="B214" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="B214" s="5" t="s">
+      <c r="C214" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="C214" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="D214" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="5" t="s">
+      <c r="D214" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="215" customHeight="1" ht="17.25">
+      <c r="A215" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B215" s="5" t="s">
+      <c r="B215" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="C215" s="6" t="s">
+      <c r="C215" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="D215" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="5" t="s">
+      <c r="D215" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="216" customHeight="1" ht="17.25">
+      <c r="A216" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="B216" s="5" t="s">
+      <c r="B216" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="C216" s="6" t="s">
+      <c r="C216" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="D216" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="5" t="s">
+      <c r="D216" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="217" customHeight="1" ht="17.25">
+      <c r="A217" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B217" s="5" t="s">
+      <c r="B217" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="C217" s="6" t="s">
+      <c r="C217" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="218" customHeight="1" ht="17.25">
+      <c r="A218" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="D217" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="5" t="s">
+      <c r="B218" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="B218" s="5" t="s">
+      <c r="C218" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="219" customHeight="1" ht="17.25">
+      <c r="A219" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="C218" s="6" t="s">
+      <c r="B219" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="D218" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="5" t="s">
+      <c r="C219" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="B219" s="5" t="s">
+      <c r="D219" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="220" customHeight="1" ht="17.25">
+      <c r="A220" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="C219" s="6" t="s">
-        <v>621</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="5" t="s">
+      <c r="B220" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="B220" s="5" t="s">
+      <c r="C220" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="C220" s="6" t="s">
-        <v>547</v>
-      </c>
-      <c r="D220" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="5" t="s">
+      <c r="D220" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="221" customHeight="1" ht="17.25">
+      <c r="A221" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="B221" s="5" t="s">
+      <c r="B221" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="222" customHeight="1" ht="17.25">
+      <c r="A222" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="C221" s="6" t="s">
+      <c r="B222" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="D221" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="5" t="s">
+      <c r="C222" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="B222" s="5" t="s">
+      <c r="D222" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="223" customHeight="1" ht="17.25">
+      <c r="A223" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="C222" s="6" t="s">
+      <c r="B223" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="D222" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="5" t="s">
+      <c r="C223" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="B223" s="5" t="s">
-        <v>564</v>
-      </c>
-      <c r="C223" s="6" t="s">
-        <v>565</v>
-      </c>
-      <c r="D223" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="B224" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="C224" s="6" t="s">
-        <v>635</v>
-      </c>
-      <c r="D224" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="5" t="s">
-        <v>636</v>
-      </c>
-      <c r="B225" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="C225" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="D225" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+      <c r="D223" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="C2"/>
-    <hyperlink r:id="rId2" ref="C3"/>
-    <hyperlink r:id="rId3" ref="C4"/>
-    <hyperlink r:id="rId4" ref="C5"/>
-    <hyperlink r:id="rId5" ref="C6"/>
-    <hyperlink r:id="rId6" ref="C7"/>
-    <hyperlink r:id="rId7" ref="C8"/>
-    <hyperlink r:id="rId8" ref="C9"/>
-    <hyperlink r:id="rId9" ref="C10"/>
-    <hyperlink r:id="rId10" ref="C11"/>
-    <hyperlink r:id="rId11" ref="C12"/>
-    <hyperlink r:id="rId12" ref="C13"/>
-    <hyperlink r:id="rId13" ref="C14"/>
-    <hyperlink r:id="rId14" ref="C15"/>
-    <hyperlink r:id="rId15" ref="C16"/>
-    <hyperlink r:id="rId16" ref="C17"/>
-    <hyperlink r:id="rId17" ref="C18"/>
-    <hyperlink r:id="rId18" ref="C19"/>
-    <hyperlink r:id="rId19" ref="C20"/>
-    <hyperlink r:id="rId20" ref="C21"/>
-    <hyperlink r:id="rId21" ref="C22"/>
-    <hyperlink r:id="rId22" ref="C23"/>
-    <hyperlink r:id="rId23" ref="C24"/>
-    <hyperlink r:id="rId24" ref="C25"/>
-    <hyperlink r:id="rId25" ref="C26"/>
-    <hyperlink r:id="rId26" ref="C27"/>
-    <hyperlink r:id="rId27" ref="C28"/>
-    <hyperlink r:id="rId28" ref="C29"/>
-    <hyperlink r:id="rId29" ref="C30"/>
-    <hyperlink r:id="rId30" ref="C31"/>
-    <hyperlink r:id="rId31" ref="C32"/>
-    <hyperlink r:id="rId32" ref="C33"/>
-    <hyperlink r:id="rId33" ref="C34"/>
-    <hyperlink r:id="rId34" ref="C35"/>
-    <hyperlink r:id="rId35" ref="C36"/>
-    <hyperlink r:id="rId36" ref="C37"/>
-    <hyperlink r:id="rId37" ref="C38"/>
-    <hyperlink r:id="rId38" ref="C39"/>
-    <hyperlink r:id="rId39" ref="C40"/>
-    <hyperlink r:id="rId40" ref="C41"/>
-    <hyperlink r:id="rId41" ref="C42"/>
-    <hyperlink r:id="rId42" ref="C43"/>
-    <hyperlink r:id="rId43" ref="C44"/>
-    <hyperlink r:id="rId44" ref="C45"/>
-    <hyperlink r:id="rId45" ref="C46"/>
-    <hyperlink r:id="rId46" ref="C47"/>
-    <hyperlink r:id="rId47" ref="C48"/>
-    <hyperlink r:id="rId48" ref="C49"/>
-    <hyperlink r:id="rId49" ref="C50"/>
-    <hyperlink r:id="rId50" ref="C51"/>
-    <hyperlink r:id="rId51" ref="C52"/>
-    <hyperlink r:id="rId52" ref="C53"/>
-    <hyperlink r:id="rId53" ref="C54"/>
-    <hyperlink r:id="rId54" ref="C55"/>
-    <hyperlink r:id="rId55" ref="C56"/>
-    <hyperlink r:id="rId56" ref="C57"/>
-    <hyperlink r:id="rId57" ref="C58"/>
-    <hyperlink r:id="rId58" ref="C59"/>
-    <hyperlink r:id="rId59" ref="C60"/>
-    <hyperlink r:id="rId60" ref="C61"/>
-    <hyperlink r:id="rId61" ref="C62"/>
-    <hyperlink r:id="rId62" ref="C63"/>
-    <hyperlink r:id="rId63" ref="C64"/>
-    <hyperlink r:id="rId64" ref="C65"/>
-    <hyperlink r:id="rId65" ref="C66"/>
-    <hyperlink r:id="rId66" ref="C67"/>
-    <hyperlink r:id="rId67" ref="C68"/>
-    <hyperlink r:id="rId68" ref="C69"/>
-    <hyperlink r:id="rId69" ref="C70"/>
-    <hyperlink r:id="rId70" ref="C71"/>
-    <hyperlink r:id="rId71" ref="C72"/>
-    <hyperlink r:id="rId72" ref="C73"/>
-    <hyperlink r:id="rId73" ref="C74"/>
-    <hyperlink r:id="rId74" ref="C75"/>
-    <hyperlink r:id="rId75" ref="C76"/>
-    <hyperlink r:id="rId76" ref="C77"/>
-    <hyperlink r:id="rId77" ref="C78"/>
-    <hyperlink r:id="rId78" ref="C79"/>
-    <hyperlink r:id="rId79" ref="C80"/>
-    <hyperlink r:id="rId80" ref="C81"/>
-    <hyperlink r:id="rId81" ref="C82"/>
-    <hyperlink r:id="rId82" ref="C83"/>
-    <hyperlink r:id="rId83" ref="C84"/>
-    <hyperlink r:id="rId84" ref="C85"/>
-    <hyperlink r:id="rId85" ref="C86"/>
-    <hyperlink r:id="rId86" ref="C87"/>
-    <hyperlink r:id="rId87" ref="C88"/>
-    <hyperlink r:id="rId88" ref="C89"/>
-    <hyperlink r:id="rId89" ref="C90"/>
-    <hyperlink r:id="rId90" ref="C91"/>
-    <hyperlink r:id="rId91" ref="C92"/>
-    <hyperlink r:id="rId92" ref="C93"/>
-    <hyperlink r:id="rId93" ref="C94"/>
-    <hyperlink r:id="rId94" ref="C95"/>
-    <hyperlink r:id="rId95" ref="C96"/>
-    <hyperlink r:id="rId96" ref="C97"/>
-    <hyperlink r:id="rId97" ref="C98"/>
-    <hyperlink r:id="rId98" ref="C99"/>
-    <hyperlink r:id="rId99" ref="C100"/>
-    <hyperlink r:id="rId100" ref="C101"/>
-    <hyperlink r:id="rId101" ref="C102"/>
-    <hyperlink r:id="rId102" ref="C103"/>
-    <hyperlink r:id="rId103" location="Uriyadi" ref="C104"/>
-    <hyperlink r:id="rId104" ref="C105"/>
-    <hyperlink r:id="rId105" ref="C106"/>
-    <hyperlink r:id="rId106" ref="C107"/>
-    <hyperlink r:id="rId107" ref="C108"/>
-    <hyperlink r:id="rId108" ref="C109"/>
-    <hyperlink r:id="rId109" ref="C110"/>
-    <hyperlink r:id="rId110" ref="C111"/>
-    <hyperlink r:id="rId111" ref="C112"/>
-    <hyperlink r:id="rId112" ref="C113"/>
-    <hyperlink r:id="rId113" ref="C114"/>
-    <hyperlink r:id="rId114" ref="C115"/>
-    <hyperlink r:id="rId115" ref="C116"/>
-    <hyperlink r:id="rId116" ref="C117"/>
-    <hyperlink r:id="rId117" ref="C118"/>
-    <hyperlink r:id="rId118" ref="C119"/>
-    <hyperlink r:id="rId119" ref="C120"/>
-    <hyperlink r:id="rId120" ref="C121"/>
-    <hyperlink r:id="rId121" ref="C122"/>
-    <hyperlink r:id="rId122" ref="C123"/>
-    <hyperlink r:id="rId123" ref="C124"/>
-    <hyperlink r:id="rId124" ref="C125"/>
-    <hyperlink r:id="rId125" ref="C126"/>
-    <hyperlink r:id="rId126" ref="C127"/>
-    <hyperlink r:id="rId127" ref="C128"/>
-    <hyperlink r:id="rId128" ref="C129"/>
-    <hyperlink r:id="rId129" ref="C130"/>
-    <hyperlink r:id="rId130" ref="C131"/>
-    <hyperlink r:id="rId131" ref="C132"/>
-    <hyperlink r:id="rId132" ref="C133"/>
-    <hyperlink r:id="rId133" ref="C134"/>
-    <hyperlink r:id="rId134" ref="C135"/>
-    <hyperlink r:id="rId135" ref="C136"/>
-    <hyperlink r:id="rId136" ref="C137"/>
-    <hyperlink r:id="rId137" ref="C138"/>
-    <hyperlink r:id="rId138" ref="C139"/>
-    <hyperlink r:id="rId139" ref="C140"/>
-    <hyperlink r:id="rId140" ref="C141"/>
-    <hyperlink r:id="rId141" ref="C142"/>
-    <hyperlink r:id="rId142" ref="C143"/>
-    <hyperlink r:id="rId143" ref="C144"/>
-    <hyperlink r:id="rId144" ref="C145"/>
-    <hyperlink r:id="rId145" ref="C146"/>
-    <hyperlink r:id="rId146" ref="C147"/>
-    <hyperlink r:id="rId147" ref="C148"/>
-    <hyperlink r:id="rId148" ref="C149"/>
-    <hyperlink r:id="rId149" ref="C150"/>
-    <hyperlink r:id="rId150" ref="C151"/>
-    <hyperlink r:id="rId151" ref="C152"/>
-    <hyperlink r:id="rId152" ref="C153"/>
-    <hyperlink r:id="rId153" ref="C154"/>
-    <hyperlink r:id="rId154" ref="C155"/>
-    <hyperlink r:id="rId155" ref="C156"/>
-    <hyperlink r:id="rId156" location=":~:text=Table_title:%20State%20Symbols%20Table_content:%20header:%20%7C%20Title,Chengaandhal%20செங்காந்தள்%20Flame%20Lily%20Gloriosa%20superba%20%7C" ref="C157"/>
-    <hyperlink r:id="rId157" ref="C158"/>
-    <hyperlink r:id="rId158" ref="C159"/>
-    <hyperlink r:id="rId159" ref="C160"/>
-    <hyperlink r:id="rId160" ref="C161"/>
-    <hyperlink r:id="rId161" ref="C162"/>
-    <hyperlink r:id="rId162" ref="C163"/>
-    <hyperlink r:id="rId163" ref="C164"/>
-    <hyperlink r:id="rId164" ref="C165"/>
-    <hyperlink r:id="rId165" ref="C166"/>
-    <hyperlink r:id="rId166" ref="C167"/>
-    <hyperlink r:id="rId167" ref="C168"/>
-    <hyperlink r:id="rId168" ref="C169"/>
-    <hyperlink r:id="rId169" ref="C170"/>
-    <hyperlink r:id="rId170" ref="C171"/>
-    <hyperlink r:id="rId171" ref="C172"/>
-    <hyperlink r:id="rId172" ref="C173"/>
-    <hyperlink r:id="rId173" ref="C174"/>
-    <hyperlink r:id="rId174" ref="C175"/>
-    <hyperlink r:id="rId175" ref="C176"/>
-    <hyperlink r:id="rId176" ref="C177"/>
-    <hyperlink r:id="rId177" ref="C178"/>
-    <hyperlink r:id="rId178" ref="C179"/>
-    <hyperlink r:id="rId179" ref="C180"/>
-    <hyperlink r:id="rId180" ref="C181"/>
-    <hyperlink r:id="rId181" ref="C182"/>
-    <hyperlink r:id="rId182" ref="C183"/>
-    <hyperlink r:id="rId183" ref="C184"/>
-    <hyperlink r:id="rId184" ref="C185"/>
-    <hyperlink r:id="rId185" ref="C186"/>
-    <hyperlink r:id="rId186" ref="C187"/>
-    <hyperlink r:id="rId187" ref="C188"/>
-    <hyperlink r:id="rId188" ref="C189"/>
-    <hyperlink r:id="rId189" ref="C190"/>
-    <hyperlink r:id="rId190" ref="C191"/>
-    <hyperlink r:id="rId191" ref="C192"/>
-    <hyperlink r:id="rId192" ref="C193"/>
-    <hyperlink r:id="rId193" ref="C194"/>
-    <hyperlink r:id="rId194" ref="C195"/>
-    <hyperlink r:id="rId195" ref="C196"/>
-    <hyperlink r:id="rId196" ref="C197"/>
-    <hyperlink r:id="rId197" ref="C198"/>
-    <hyperlink r:id="rId198" ref="C199"/>
-    <hyperlink r:id="rId199" ref="C200"/>
-    <hyperlink r:id="rId200" ref="C201"/>
-    <hyperlink r:id="rId201" ref="C202"/>
-    <hyperlink r:id="rId202" ref="C203"/>
-    <hyperlink r:id="rId203" ref="C204"/>
-    <hyperlink r:id="rId204" ref="C205"/>
-    <hyperlink r:id="rId205" ref="C206"/>
-    <hyperlink r:id="rId206" ref="C207"/>
-    <hyperlink r:id="rId207" ref="C208"/>
-    <hyperlink r:id="rId208" ref="C209"/>
-    <hyperlink r:id="rId209" ref="C210"/>
-    <hyperlink r:id="rId210" ref="C211"/>
-    <hyperlink r:id="rId211" ref="C212"/>
-    <hyperlink r:id="rId212" ref="C213"/>
-    <hyperlink r:id="rId213" ref="C214"/>
-    <hyperlink r:id="rId214" ref="C215"/>
-    <hyperlink r:id="rId215" ref="C216"/>
-    <hyperlink r:id="rId216" ref="C217"/>
-    <hyperlink r:id="rId217" ref="C218"/>
-    <hyperlink r:id="rId218" ref="C219"/>
-    <hyperlink r:id="rId219" ref="C220"/>
-    <hyperlink r:id="rId220" ref="C221"/>
-    <hyperlink r:id="rId221" ref="C222"/>
-    <hyperlink r:id="rId222" ref="C223"/>
-    <hyperlink r:id="rId223" ref="C224"/>
-    <hyperlink r:id="rId224" ref="C225"/>
-  </hyperlinks>
-  <drawing r:id="rId225"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datasets/IndicWikiQA-Tam_EN.xlsx
+++ b/datasets/IndicWikiQA-Tam_EN.xlsx
@@ -565,7 +565,7 @@
     <t>Which sweet, steamed dumpling is traditionally offered to Pillayar during his festival?</t>
   </si>
   <si>
-    <t>Modagam</t>
+    <t>Modak (Kozhukattai)</t>
   </si>
   <si>
     <t>What tiered, thematic doll display is a central tradition in Tamil households during Navaratri?</t>
@@ -1998,7 +1998,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2311,7 +2311,7 @@
     <col min="4" max="4" style="5" width="21.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -2353,7 +2353,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -2409,7 +2409,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -2451,7 +2451,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="2" t="s">
         <v>38</v>
       </c>
@@ -2493,7 +2493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="2" t="s">
         <v>41</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="2" t="s">
         <v>44</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="2" t="s">
         <v>47</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="2" t="s">
         <v>50</v>
       </c>
@@ -2549,7 +2549,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="2" t="s">
         <v>53</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="2" t="s">
         <v>56</v>
       </c>
